--- a/src/Excelsior.Tests/NaughtyStringsTests.Test.verified.xlsx
+++ b/src/Excelsior.Tests/NaughtyStringsTests.Test.verified.xlsx
@@ -8130,7 +8130,7 @@
 </file>
 
 <file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
-<columnMetadata xmlns="https://github.com/Papyrine/Excelsior/columnMetadata/v1">
+<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
   <sheet name="Sheet1">
     <column index="1" property="Value"/>
     <column index="2" property="Html"/>

--- a/src/Excelsior.Tests/NaughtyStringsTests.Test.verified.xlsx
+++ b/src/Excelsior.Tests/NaughtyStringsTests.Test.verified.xlsx
@@ -6581,7 +6581,7 @@
             <rPr>
               <u/>
             </rPr>
-            <t xml:space="preserve"> Copy me</t>
+            <t xml:space="preserve">Copy me</t>
           </r>
         </is>
       </c>
@@ -6598,7 +6598,7 @@
             <rPr>
               <i/>
             </rPr>
-            <t xml:space="preserve"> Scroll over me </t>
+            <t xml:space="preserve">Scroll over me</t>
           </r>
         </is>
       </c>
